--- a/Proyecto/docs/TablasUnitarias/TablasUnitarias.xlsx
+++ b/Proyecto/docs/TablasUnitarias/TablasUnitarias.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/01f32f4e8c9e178e/Desktop/Analisis y Diseño/36289_AnalisisYDisenoDeSistemas/Proyecto/docs/TablasUnitarias/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uabcedumx-my.sharepoint.com/personal/joshua_osorio_uabc_edu_mx/Documents/8_Semestre/36289_AnalisisYDisenoDeSistemas/Proyecto/docs/TablasUnitarias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="291" documentId="8_{649B9B8D-9FCF-4007-A430-E9105B148E88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DAA8BF75-4196-4BFD-AD35-76D00AF3643B}"/>
+  <xr:revisionPtr revIDLastSave="293" documentId="8_{649B9B8D-9FCF-4007-A430-E9105B148E88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F43E9D8A-2D53-4220-AA2F-73FBEEB4C1E3}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15330" windowHeight="15585" activeTab="3" xr2:uid="{E9EB2947-A93B-4945-B872-2E322012306D}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E9EB2947-A93B-4945-B872-2E322012306D}"/>
   </bookViews>
   <sheets>
     <sheet name="Usuario" sheetId="1" r:id="rId1"/>
@@ -488,10 +488,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1409,7 +1405,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{666B8B33-5216-49B1-964C-89A77804578C}">
-  <dimension ref="B2:H49"/>
+  <dimension ref="B2:J49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.5703125" customWidth="1"/>
@@ -1421,7 +1417,7 @@
     <col min="8" max="8" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
@@ -1438,7 +1434,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C3" s="1" t="s">
         <v>61</v>
       </c>
@@ -1455,7 +1451,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C4" s="1" t="s">
         <v>61</v>
       </c>
@@ -1472,7 +1468,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C5" s="1" t="s">
         <v>61</v>
       </c>
@@ -1489,7 +1485,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C6" s="1" t="s">
         <v>61</v>
       </c>
@@ -1506,7 +1502,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C7" s="1" t="s">
         <v>61</v>
       </c>
@@ -1521,7 +1517,7 @@
       </c>
       <c r="H7" s="10"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C8" s="1" t="s">
         <v>61</v>
       </c>
@@ -1536,12 +1532,12 @@
       </c>
       <c r="H8" s="10"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="H9" s="10" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
         <v>17</v>
       </c>
@@ -1561,7 +1557,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C11" s="5" t="s">
         <v>61</v>
       </c>
@@ -1578,7 +1574,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C12" s="5" t="s">
         <v>61</v>
       </c>
@@ -1592,7 +1588,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C13" s="5" t="s">
         <v>61</v>
       </c>
@@ -1606,7 +1602,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C14" s="5" t="s">
         <v>61</v>
       </c>
@@ -1620,7 +1616,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C15" s="5" t="s">
         <v>61</v>
       </c>
@@ -1634,7 +1630,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C16" s="5" t="s">
         <v>61</v>
       </c>
@@ -1647,16 +1643,16 @@
       <c r="F16" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="H16" t="s">
+      <c r="J16" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="G17" t="s">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J17" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
         <v>5</v>
       </c>
@@ -1672,11 +1668,11 @@
       <c r="F18" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G18" t="s">
+      <c r="J18" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C19" s="1" t="s">
         <v>75</v>
       </c>
@@ -1689,11 +1685,11 @@
       <c r="F19" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G19" t="s">
+      <c r="J19" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C20" s="1" t="s">
         <v>75</v>
       </c>
@@ -1706,11 +1702,11 @@
       <c r="F20" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G20" t="s">
+      <c r="J20" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C21" s="1" t="s">
         <v>75</v>
       </c>
@@ -1724,7 +1720,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C22" s="1" t="s">
         <v>75</v>
       </c>
@@ -1738,7 +1734,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C23" s="1" t="s">
         <v>75</v>
       </c>
@@ -1752,7 +1748,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C24" s="1" t="s">
         <v>75</v>
       </c>
@@ -1766,7 +1762,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="4" t="s">
         <v>17</v>
       </c>
@@ -1783,7 +1779,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C27" s="5" t="s">
         <v>75</v>
       </c>
@@ -1797,7 +1793,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C28" s="5" t="s">
         <v>75</v>
       </c>
@@ -1811,7 +1807,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C29" s="5" t="s">
         <v>75</v>
       </c>
@@ -1825,7 +1821,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C30" s="5" t="s">
         <v>75</v>
       </c>
@@ -1839,7 +1835,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C31" s="5" t="s">
         <v>75</v>
       </c>
@@ -1853,7 +1849,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C32" s="5" t="s">
         <v>75</v>
       </c>
